--- a/artfynd/A 34678-2022 artfynd.xlsx
+++ b/artfynd/A 34678-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 34678-2022 artfynd.xlsx
+++ b/artfynd/A 34678-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>62055369</v>
+        <v>62055367</v>
       </c>
       <c r="B2" t="n">
-        <v>90638</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1968</v>
+        <v>112</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grantaggsvamp</t>
+          <t>Stjärntagging</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bankera violascens</t>
+          <t>Asterodon ferruginosus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein. : Fr.) Pouzar</t>
+          <t>Pat.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>478638.8089161717</v>
+        <v>478696</v>
       </c>
       <c r="R2" t="n">
-        <v>7028951.10102236</v>
+        <v>7029080</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,14 @@
           <t>2002-08-22</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2002-08-22</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Åssluttning mot nordöstra sidan av Äsmyren, ca 2,5 km nordväst om Nävrans utlopp i Långan,</t>
+          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Mellan skogsbilväg och Bötelsmyrens sydvästra flank, ca 2,5 km nordväst om Nävrans utlopp i Långan,</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -776,6 +761,16 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Björklåga,</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Björklåga,</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -796,15 +791,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>62055429</v>
+        <v>62055372</v>
       </c>
       <c r="B3" t="n">
-        <v>90647</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>88404</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -812,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4362</v>
+        <v>170</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Sumpäggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Bovista paludosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>Lév.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -836,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>478630.9879953872</v>
+        <v>478596</v>
       </c>
       <c r="R3" t="n">
-        <v>7028990.160961268</v>
+        <v>7028970</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,24 +859,14 @@
           <t>2002-08-22</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2002-08-22</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Mellan skogsbilväg och Äsmyrens nordöstra sida, ca 2,5 km nordväst om Nävrans utlopp i Långan,</t>
+          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Äsmyren, ca 2,6 km nordväst om Nävrans utlopp i Långan, ca 1,2 km sydsydost om Libodarna,</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>62055359</v>
+        <v>101955</v>
       </c>
       <c r="B4" t="n">
-        <v>90669</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83302</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -933,43 +908,36 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2059</v>
+        <v>310</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Skrovlig taggsvamp</t>
+          <t>Nordlig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum scabrosum</t>
+          <t>Chaenotheca laevigata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>Nádv.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Bötelsmyren - Äsmyren - Källmyren, Jmt</t>
+          <t>Källmyren, S fastmarkskanten vid Bötelsmyrens Vra utlöpare,, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>478618.600014712</v>
+        <v>478790</v>
       </c>
       <c r="R4" t="n">
-        <v>7029017.593631543</v>
+        <v>7028995</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -999,26 +967,11 @@
           <t>2000-09-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2000-09-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>1 ex. Ursprungligen bestämd till blåfotad taggsvamp (leg/det Johan Nitare). 2000: Inom några kvadratmeter även goliatmusseron, skarp dropptaggsvamp, skavfräken, slåtterfibbla, kattfot m.m. Även funnen ca 100 m sydost om denna plats 2001. Äsmyren, vid nordöstra sidan,</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1027,16 +980,26 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>Granskog nära myrkant,</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Ca 1,5 m hög björkstubbe &lt; 2 dm i diam.</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>malin almquist</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Bengt Petterson, Johan Nitare</t>
+          <t>Göran Eriksson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1047,59 +1010,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>62055722</v>
+        <v>62055419</v>
       </c>
       <c r="B5" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6276</v>
+        <v>510</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bötelsmyren - Äsmyren - Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>478677.9510000038</v>
+        <v>478782</v>
       </c>
       <c r="R5" t="n">
-        <v>7028828.433455745</v>
+        <v>7029000</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1129,24 +1078,14 @@
           <t>2002-08-22</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2002-08-22</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>3 ex. 1 ex. goliat funnen 2002-08-22, 2ex. funna i mitten av oktober / LR/. Äldsta tall 148 år, medelålder 124 år.Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Vid nordöstra sidan av Äsmyren, ca 2,5 km nordväst om Nävrans utlopp i Långan, ca 1350 m sydsydost om Libodarna, ca 75 m söder om skogsbilvägs vändplan,</t>
+          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Vid västra kanten av Bötelsmyrens sydvästra flank, ca 2,4 km nordväst om Nävrans utlopp i Långan,</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1157,6 +1096,16 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1177,37 +1126,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>62055357</v>
+        <v>62055689</v>
       </c>
       <c r="B6" t="n">
-        <v>88019</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91920</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6276</v>
+        <v>1205</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Stor aspticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Phellinus populicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1217,10 +1161,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>478618.600014712</v>
+        <v>478854</v>
       </c>
       <c r="R6" t="n">
-        <v>7029017.593631543</v>
+        <v>7028941</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1247,37 +1191,37 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2006-09-24</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-08-22</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2006-09-24</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-08-22</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>0. Sökt ej funnen. Dåligt med svamp i området. Äsmyren, vid nordöstra sidan,</t>
+          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Mellan skogsbilväg och sydvästra sidan av Bötelsmyrens sydvästra flank. ca 2,3 km nordväst om Nävrans utlopp i Långan,</t>
         </is>
       </c>
       <c r="AD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
       <c r="AG6" t="b">
         <v>0</v>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Asp</t>
+        </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
@@ -1298,50 +1242,49 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>62055419</v>
+        <v>397459</v>
       </c>
       <c r="B7" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101935</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>1448</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Myrbräcka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Saxifraga hirculus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>5000</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Bötelsmyren - Äsmyren - Källmyren, Jmt</t>
+          <t>Äsmyren S delen, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>478781.9060695134</v>
+        <v>478636</v>
       </c>
       <c r="R7" t="n">
-        <v>7028999.918241248</v>
+        <v>7028818</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1368,27 +1311,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>1993-08-05</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Vid västra kanten av Bötelsmyrens sydvästra flank, ca 2,4 km nordväst om Nävrans utlopp i Långan,</t>
+          <t>1993-08-05</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1400,82 +1328,72 @@
       <c r="AG7" t="b">
         <v>0</v>
       </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>Rikkärr</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Staffan Åström</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>62055367</v>
+        <v>118124858</v>
       </c>
       <c r="B8" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101935</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>112</v>
+        <v>1448</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stjärntagging</t>
+          <t>Myrbräcka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Asterodon ferruginosus</t>
+          <t>Saxifraga hirculus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Pat.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Bötelsmyren - Äsmyren - Källmyren, Jmt</t>
+          <t>Äsmyren, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>478695.7871277012</v>
+        <v>478647</v>
       </c>
       <c r="R8" t="n">
-        <v>7029079.848830959</v>
+        <v>7028795</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1499,27 +1417,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2002-08-22</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Mellan skogsbilväg och Bötelsmyrens sydvästra flank, ca 2,5 km nordväst om Nävrans utlopp i Långan,</t>
+          <t>2024-06-30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1528,69 +1431,51 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>Björklåga,</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>Björklåga,</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Lars-Åke Bäckström</t>
+          <t>Gunnar Kvarnlöf</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Bengt Petterson</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Lst Z Artdatabas</t>
-        </is>
-      </c>
+          <t>Gunnar Kvarnlöf</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>62055708</v>
+        <v>62055369</v>
       </c>
       <c r="B9" t="n">
-        <v>89732</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93231</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>1968</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Grantaggsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellodon violascens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) A.M.Ainsw.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1600,13 +1485,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>478768.699200809</v>
+        <v>478639</v>
       </c>
       <c r="R9" t="n">
-        <v>7029039.461268582</v>
+        <v>7028951</v>
       </c>
       <c r="S9" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1633,24 +1518,14 @@
           <t>2002-08-22</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2002-08-22</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>Bötelsmyren, åssluttning söder om sydvästra flanken,</t>
+          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Åssluttning mot nordöstra sidan av Äsmyren, ca 2,5 km nordväst om Nävrans utlopp i Långan,</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1661,16 +1536,6 @@
       </c>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>Granlåga / Ullticka</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Granlåga / Ullticka</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
@@ -1691,52 +1556,54 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>101955</v>
+        <v>62055359</v>
       </c>
       <c r="B10" t="n">
-        <v>73689</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93213</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>310</v>
+        <v>2059</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Nordlig nållav</t>
+          <t>Skrovlig taggsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Chaenotheca laevigata</t>
+          <t>Hydnellum scabrosum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Nádv.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+          <t>(Fr.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Källmyren, S fastmarkskanten vid Bötelsmyrens Vra utlöpare,, Jmt</t>
+          <t>Bötelsmyren - Äsmyren - Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>478789.954460423</v>
+        <v>478619</v>
       </c>
       <c r="R10" t="n">
-        <v>7028994.932958394</v>
+        <v>7029018</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1766,19 +1633,14 @@
           <t>2000-09-18</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2000-09-18</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1 ex. Ursprungligen bestämd till blåfotad taggsvamp (leg/det Johan Nitare). 2000: Inom några kvadratmeter även goliatmusseron, skarp dropptaggsvamp, skavfräken, slåtterfibbla, kattfot m.m. Även funnen ca 100 m sydost om denna plats 2001. Äsmyren, vid nordöstra sidan,</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1789,26 +1651,16 @@
       </c>
       <c r="AG10" t="b">
         <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>Granskog nära myrkant,</t>
-        </is>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>Ca 1,5 m hög björkstubbe &lt; 2 dm i diam.</t>
-        </is>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>malin almquist</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Göran Eriksson</t>
+          <t>Bengt Petterson, Johan Nitare</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
@@ -1819,57 +1671,48 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>103121429</v>
+        <v>62055708</v>
       </c>
       <c r="B11" t="n">
-        <v>103265</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92281</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>221144</v>
+        <v>2062</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Aspås, Lillsjön, Aspås, Jmt</t>
+          <t>Bötelsmyren - Äsmyren - Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>478675.3443639741</v>
+        <v>478769</v>
       </c>
       <c r="R11" t="n">
-        <v>7028976.414416077</v>
+        <v>7029039</v>
       </c>
       <c r="S11" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1893,22 +1736,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-08-22</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Bötelsmyren, åssluttning söder om sydvästra flanken,</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1917,76 +1755,80 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>Granlåga / Ullticka</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>Granlåga / Ullticka</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>103121475</v>
+        <v>62055429</v>
       </c>
       <c r="B12" t="n">
-        <v>95525</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93191</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>221941</v>
+        <v>4362</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Aspås, Lillsjön, Aspås, Jmt</t>
+          <t>Bötelsmyren - Äsmyren - Källmyren, Jmt</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>478554.9546764187</v>
+        <v>478631</v>
       </c>
       <c r="R12" t="n">
-        <v>7029167.767476318</v>
+        <v>7028990</v>
       </c>
       <c r="S12" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2010,22 +1852,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-08-22</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2022-08-23</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Mellan skogsbilväg och Äsmyrens nordöstra sida, ca 2,5 km nordväst om Nävrans utlopp i Långan,</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2034,22 +1871,591 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
+          <t>Lars-Åke Bäckström</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Rashid Kadhim</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>62055356</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bötelsmyren - Äsmyren - Källmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>478619</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7029018</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2000-09-02</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2000-09-02</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>1 ex. Inom några kvadratmeter även skrovlig taggsvamp, skarp dropptaggsvamp, skavfräken, slåtterfibbla, kattfot m.m. Äsmyren, vid nordöstra sidan,</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Staffan Åström, Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>62055722</v>
+      </c>
+      <c r="B14" t="n">
+        <v>90691</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6276</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Goliatmusseron</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Tricholoma matsutake</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bötelsmyren - Äsmyren - Källmyren, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>478678</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7028828</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2002-08-22</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>3 ex. 1 ex. goliat funnen 2002-08-22, 2ex. funna i mitten av oktober / LR/. Äldsta tall 148 år, medelålder 124 år.Inventerat område; Ca 15 ha äldre skog mellan Äsmyrens nordöstra sida - Bötelsmyrens sydvästra sida och Nävrans norra sida ner till gångbron inkl. närmast angränsande delar av Äsmyren och Bötelsmyren. Båda sidor om ny skogsbilväg och nordost - söder om vändplan. ÖMF / Västgötabergens Svampvänner Vid nordöstra sidan av Äsmyren, ca 2,5 km nordväst om Nävrans utlopp i Långan, ca 1350 m sydsydost om Libodarna, ca 75 m söder om skogsbilvägs vändplan,</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Lars-Åke Bäckström</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bengt Petterson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Lst Z Artdatabas</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>56844210</v>
+      </c>
+      <c r="B15" t="n">
+        <v>61741</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>101966</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Otandad grynsnäcka</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Vertigo genesii</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Gredler, 1856)</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Äsmyran, Mellan Nävran och Långan, 2 km uppströms sammanflödet, Jmt</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>478654</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7028801</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2001-07-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2001-07-22</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>5 ex./Övriga arter: V. lilljeborgi, V. substriata, Vallonia m.fl.; Växter: Carex lasiocarpa, Scorpidium cossonii; Trädskilkt: ; Lokalbeskr: Mellan Nävran och Långan, 2 km uppströms sammanflödet</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>kärrgolv/Övriga arter: V. lilljeborgi, V. substriata, Vallonia m.fl.; Växter: Carex lasiocarpa, Scorpidium cossonii; Trädskilkt:</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>56844211</v>
+      </c>
+      <c r="B16" t="n">
+        <v>61741</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>101966</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Otandad grynsnäcka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Vertigo genesii</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Gredler, 1856)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Äsmyran. Mellan Nävran och Långan, 2 km uppströms sammanflödet., Jmt</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>478602</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7028979</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2001-07-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2001-07-22</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>11 ex./Övriga arter: Cochlicopa m.fl.; Växter: Phragmites australis, Scorpidium cossonii i sänkor, Sphagnum fuscum och S. warnstorfii i tuvorna; Trädskilkt: ; Lokalbeskr: Mellan Nävran och Långan, 2 km uppströms sammanflödet</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>kärrgolv, tuvigt/Övriga arter: Cochlicopa m.fl.; Växter: Phragmites australis, Scorpidium cossonii i sänkor, Sphagnum fuscum och S. warnstorfii i tuvorna; Trädskilkt:</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kristoffer Hylander</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>61075676</v>
+      </c>
+      <c r="B17" t="n">
+        <v>99049</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>219794</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Sumpnycklar</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dactylorhiza majalis subsp. lapponica</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Laest. ex Hartm.) H. Sund.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Äsmyren, ca 2,5 km nordväst om Nävrans utlopp i Långan, ca  1,3 km sydsydos, Jmt</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>478643</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7028828</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Aspås</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2002-07-15</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2002-07-15</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Rikkärr</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Staffan Åström</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Bengt-Göran Carlsson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 34678-2022 artfynd.xlsx
+++ b/artfynd/A 34678-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -788,6 +793,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055367</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055372</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1007,6 +1022,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101955</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1123,6 +1143,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055419</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1239,6 +1264,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055689</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1345,6 +1375,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/397459</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1447,6 +1482,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118124858</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1553,6 +1593,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055369</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1668,6 +1713,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055359</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1784,6 +1834,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055708</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1890,6 +1945,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055429</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2005,6 +2065,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055356</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2120,6 +2185,11 @@
           <t>Lst Z Artdatabas</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62055722</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2237,6 +2307,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56844210</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2354,6 +2429,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/56844211</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2456,8 +2536,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/61075676</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>